--- a/docs/database/import-templates/DB-11-session-recaps.xlsx
+++ b/docs/database/import-templates/DB-11-session-recaps.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc248fea15b1d4305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4dde0c37c204fb1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -660,7 +660,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -682,14 +682,6 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:alignment vertical="center"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -701,14 +693,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -721,14 +705,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -783,23 +759,6 @@
     <x:cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1028,167 +987,167 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="13" t="s">
+      <x:c r="A1" s="11" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="s">
+      <x:c r="B1" s="12" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="s">
+      <x:c r="C1" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="s">
+      <x:c r="D1" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="15" t="s">
+      <x:c r="E1" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="14" t="str">
         <x:v>session_id</x:v>
       </x:c>
-      <x:c r="B2" s="16" t="str">
+      <x:c r="B2" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="14" t="str">
         <x:v>会话业务标识</x:v>
       </x:c>
-      <x:c r="D2" s="16"/>
-      <x:c r="E2" s="17" t="b">
-        <x:v>1</x:v>
+      <x:c r="D2" s="14"/>
+      <x:c r="E2" s="14" t="str">
+        <x:v>是</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="14" t="str">
         <x:v>user_recap_json</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C3" s="16" t="str">
+      <x:c r="C3" s="14" t="str">
         <x:v>给用户看的复盘 JSON</x:v>
       </x:c>
-      <x:c r="D3" s="16" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>{}</x:v>
       </x:c>
-      <x:c r="E3" s="17" t="b">
-        <x:v>1</x:v>
+      <x:c r="E3" s="14" t="str">
+        <x:v>是</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="14" t="str">
         <x:v>agent_recap_json</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="14" t="str">
         <x:v>给 Agent 续接的复盘 JSON</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="str">
+      <x:c r="D4" s="14" t="str">
         <x:v>{}</x:v>
       </x:c>
-      <x:c r="E4" s="17" t="b">
-        <x:v>1</x:v>
+      <x:c r="E4" s="14" t="str">
+        <x:v>是</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="14" t="str">
         <x:v>new_facts_json</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="14" t="str">
         <x:v>本轮新增且允许保存的事实</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="14" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="E5" s="17" t="b">
-        <x:v>0</x:v>
+      <x:c r="E5" s="14" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="14" t="str">
         <x:v>state_changes_json</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B6" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="str">
+      <x:c r="C6" s="14" t="str">
         <x:v>本轮成功发生的状态变化</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="str">
+      <x:c r="D6" s="14" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="E6" s="17" t="b">
-        <x:v>0</x:v>
+      <x:c r="E6" s="14" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" s="14" t="str">
         <x:v>open_questions_json</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
+      <x:c r="B7" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="str">
+      <x:c r="C7" s="14" t="str">
         <x:v>未决问题 JSON</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="str">
+      <x:c r="D7" s="14" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="b">
-        <x:v>0</x:v>
+      <x:c r="E7" s="14" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="16" t="str">
+      <x:c r="A8" s="14" t="str">
         <x:v>next_entry</x:v>
       </x:c>
-      <x:c r="B8" s="16" t="str">
+      <x:c r="B8" s="14" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="C8" s="16" t="str">
+      <x:c r="C8" s="14" t="str">
         <x:v>下次会话建议入口</x:v>
       </x:c>
-      <x:c r="D8" s="16"/>
-      <x:c r="E8" s="17" t="b">
-        <x:v>1</x:v>
+      <x:c r="D8" s="14"/>
+      <x:c r="E8" s="14" t="str">
+        <x:v>是</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="16" t="str">
+      <x:c r="A9" s="14" t="str">
         <x:v>recap_version</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="14" t="str">
         <x:v>Integer</x:v>
       </x:c>
-      <x:c r="C9" s="16" t="str">
+      <x:c r="C9" s="14" t="str">
         <x:v>复盘版本</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="n">
+      <x:c r="D9" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E9" s="17" t="b">
-        <x:v>1</x:v>
+      <x:c r="E9" s="14" t="str">
+        <x:v>是</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="16" t="str">
+      <x:c r="A10" s="14" t="str">
         <x:v>updated_at</x:v>
       </x:c>
-      <x:c r="B10" s="16" t="str">
+      <x:c r="B10" s="14" t="str">
         <x:v>Time</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="str">
+      <x:c r="C10" s="14" t="str">
         <x:v>最后更新时间</x:v>
       </x:c>
-      <x:c r="D10" s="16"/>
-      <x:c r="E10" s="17" t="b">
-        <x:v>1</x:v>
+      <x:c r="D10" s="14"/>
+      <x:c r="E10" s="14" t="str">
+        <x:v>是</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/database/import-templates/DB-11-session-recaps.xlsx
+++ b/docs/database/import-templates/DB-11-session-recaps.xlsx
@@ -1205,7 +1205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>user_key</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>会话业务标识</t>
+          <t>MAIN 生成的会话级业务用户键</t>
         </is>
       </c>
       <c r="D2"/>
@@ -1228,7 +1228,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_recap_json</t>
+          <t>recap_id</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1238,14 +1238,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>给用户看的复盘 JSON</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
+          <t>会话收束业务标识</t>
+        </is>
+      </c>
+      <c r="D3"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>是</t>
@@ -1255,7 +1251,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>agent_recap_json</t>
+          <t>user_recap_json</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1265,7 +1261,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>给 Agent 续接的复盘 JSON</t>
+          <t>给用户看的复盘 JSON</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1282,7 +1278,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>new_facts_json</t>
+          <t>agent_recap_json</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1292,24 +1288,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>本轮新增且允许保存的事实</t>
+          <t>给 Agent 续接的复盘 JSON</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>state_changes_json</t>
+          <t>new_facts_json</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1319,7 +1315,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>本轮成功发生的状态变化</t>
+          <t>本轮新增且允许保存的事实</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1336,7 +1332,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>open_questions_json</t>
+          <t>state_changes_json</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1346,7 +1342,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>未决问题 JSON</t>
+          <t>本轮成功发生的状态变化</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1363,7 +1359,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>next_entry</t>
+          <t>open_questions_json</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1373,37 +1369,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>下次会话建议入口</t>
-        </is>
-      </c>
-      <c r="D8"/>
+          <t>未决问题 JSON</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>recap_version</t>
+          <t>next_action</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>复盘版本</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>下次建议的自然语言入口</t>
+        </is>
+      </c>
+      <c r="D9"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>是</t>
@@ -1413,20 +1409,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>record_version</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>最后更新时间</t>
-        </is>
-      </c>
-      <c r="D10"/>
+          <t>会话收束版本号</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>是</t>
